--- a/data/LCIs/Lai_2025/Graphite_LCIs_BW_Final_v1.xlsx
+++ b/data/LCIs/Lai_2025/Graphite_LCIs_BW_Final_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://brgm365.sharepoint.com/sites/RPPEXIMPMET/Documents partages/General/P2/04_Data/04_Modelling/02_LCI modelling/Gr_Graphite/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/data/LCIs/Lai_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="178" documentId="8_{4E3DD59C-3AFA-4D66-BAD6-4D8B482B0214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE8171B-4DE3-4F15-97E4-E0BCC54C54EB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" r:id="rId1"/>
@@ -1772,7 +1772,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1790,22 +1790,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1813,33 +1807,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1868,14 +1835,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2174,607 +2165,607 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="17"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="18"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="20"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="29"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B4" s="18"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="20"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="29"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="20"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="29"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="18"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="20"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="29"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="20"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="29"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="18"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="20"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="29"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="18"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="20"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="29"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="18"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="20"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="29"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="18"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="20"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="29"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="18"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="20"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="29"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="20"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="29"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="20"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="29"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="18"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="20"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="29"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="20"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="29"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="20"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="29"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B18" s="18"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="20"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="29"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="20"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="29"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B20" s="18"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="20"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="29"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B21" s="18"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="20"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="29"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="18"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="20"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="29"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B23" s="18"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="20"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="29"/>
     </row>
     <row r="24" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="18"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="20"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="28"/>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="29"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B25" s="18"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="20"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="29"/>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="18"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="20"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="29"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="18"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="20"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="29"/>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="18"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="20"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="29"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B29" s="18"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="20"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="29"/>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="18"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="20"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="29"/>
     </row>
     <row r="31" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="21"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="22"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="22"/>
-      <c r="Q31" s="23"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="32"/>
     </row>
     <row r="32" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="27"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="16"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="29"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="18"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="29"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="18"/>
     </row>
     <row r="36" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="35" t="s">
+      <c r="C36" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="32"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3128,73 +3119,73 @@
   <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="85.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="86" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="85.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="86" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3243,281 +3234,281 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="str">
+      <c r="A9" s="6" t="str">
         <f>B1</f>
         <v>[M] Graphite ore mining</v>
       </c>
-      <c r="B9" s="8" t="str">
+      <c r="B9" s="6" t="str">
         <f>B2</f>
         <v>Graphite ore</v>
       </c>
-      <c r="C9" s="8" t="str">
+      <c r="C9" s="6" t="str">
         <f>B3</f>
         <v>CN</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="6">
         <v>1</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="12" t="str">
+      <c r="F9" s="10" t="str">
         <f>Graphite_Market_GLO!B1</f>
         <v>Graphite</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <v>2.2409999999999999E-3</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="6">
         <v>2.4800000000000001E-4</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <v>1.2E-5</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>1.2219999999999999E-4</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <v>-2.5000000000000001E-5</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>1.3799999999999999E-4</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>1.1300000000000001E-7</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="6">
         <v>4.0000000000000003E-5</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>0</v>
@@ -3527,47 +3518,47 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3616,385 +3607,385 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="str">
+      <c r="A29" s="6" t="str">
         <f>B21</f>
         <v>[C] Flotation</v>
       </c>
-      <c r="B29" s="8" t="str">
+      <c r="B29" s="6" t="str">
         <f>B22</f>
         <v>Graphite concentrate</v>
       </c>
-      <c r="C29" s="8" t="str">
+      <c r="C29" s="6" t="str">
         <f>B23</f>
         <v>CN</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="6">
         <v>1</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="12" t="str">
+      <c r="F29" s="10" t="str">
         <f>F9</f>
         <v>Graphite</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="6">
         <v>0.50600000000000001</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="J30" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="6">
         <v>4.4819999999999999E-2</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="J31" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="6">
         <v>0.05</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J32" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="6">
         <v>1.163E-3</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="J33" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="6">
         <v>1.5510000000000001E-3</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J34" s="8" t="s">
+      <c r="J34" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J35" s="8" t="s">
+      <c r="J35" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="6">
         <v>1.9179999999999999E-2</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J36" s="8" t="s">
+      <c r="J36" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="6">
         <v>-1.3960000000000001E-3</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="J37" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="6">
         <v>-2.1707000000000001E-2</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="8" t="s">
+      <c r="J38" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="6">
         <v>-8.5960000000000001</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="8" t="s">
+      <c r="J39" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="6">
         <v>2.2027000000000001E-2</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J40" s="8" t="s">
+      <c r="J40" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="6">
         <v>0.183333</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J41" s="8" t="s">
+      <c r="J41" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="6">
         <v>3.2014499999999998E-4</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="8" t="s">
+      <c r="J42" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="6">
         <v>1.047E-3</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="J43" s="8" t="s">
+      <c r="J43" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>0</v>
@@ -4004,47 +3995,47 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4093,111 +4084,111 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="str">
+      <c r="A53" s="6" t="str">
         <f>B45</f>
         <v>[P+R] Spheronisation</v>
       </c>
-      <c r="B53" s="8" t="str">
+      <c r="B53" s="6" t="str">
         <f>B46</f>
         <v>Spherical graphite</v>
       </c>
-      <c r="C53" s="8" t="str">
+      <c r="C53" s="6" t="str">
         <f>B47</f>
         <v>CN</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="6">
         <v>1</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F53" s="12" t="str">
+      <c r="F53" s="10" t="str">
         <f>F29</f>
         <v>Graphite</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="G53" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="6">
         <v>2.1</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F54" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G54" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="J54" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="6">
         <v>1.8675000000000001E-2</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="F55" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G55" s="8" t="s">
+      <c r="G55" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J55" s="8" t="s">
+      <c r="J55" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="6">
         <v>-2.5000000000000001E-4</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="F56" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="G56" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J56" s="8" t="s">
+      <c r="J56" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>0</v>
@@ -4207,47 +4198,47 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="6" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4296,414 +4287,414 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="str">
+      <c r="A66" s="6" t="str">
         <f>B58</f>
         <v>[P+R] Purification</v>
       </c>
-      <c r="B66" s="8" t="str">
+      <c r="B66" s="6" t="str">
         <f>B59</f>
         <v>Purified spherical graphite</v>
       </c>
-      <c r="C66" s="8" t="str">
+      <c r="C66" s="6" t="str">
         <f>B60</f>
         <v>CN</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="6">
         <v>1</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F66" s="12" t="str">
+      <c r="F66" s="10" t="str">
         <f>F53</f>
         <v>Graphite</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="6">
         <v>0.30499999999999999</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G67" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J67" s="8" t="s">
+      <c r="J67" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="6">
         <v>1.1205E-2</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F68" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G68" s="8" t="s">
+      <c r="G68" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J68" s="8" t="s">
+      <c r="J68" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="6">
         <v>2.5862068965517241E-2</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G69" s="8" t="s">
+      <c r="G69" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J69" s="8" t="s">
+      <c r="J69" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="6">
         <v>0.18</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F70" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J70" s="8" t="s">
+      <c r="J70" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="6">
         <v>0.2</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F71" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G71" s="8" t="s">
+      <c r="G71" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J71" s="8" t="s">
+      <c r="J71" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="6">
         <v>0.1</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="F72" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G72" s="8" t="s">
+      <c r="G72" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J72" s="8" t="s">
+      <c r="J72" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="6">
         <v>0.4</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G73" s="8" t="s">
+      <c r="G73" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J73" s="8" t="s">
+      <c r="J73" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="6">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G74" s="8" t="s">
+      <c r="G74" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J74" s="8" t="s">
+      <c r="J74" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="6">
         <v>0.02</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E75" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G75" s="8" t="s">
+      <c r="G75" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J75" s="8" t="s">
+      <c r="J75" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="6">
         <v>2.751E-3</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E76" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F76" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G76" s="8" t="s">
+      <c r="G76" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J76" s="8" t="s">
+      <c r="J76" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="6">
         <v>-2.4773E-2</v>
       </c>
-      <c r="E77" s="8" t="s">
+      <c r="E77" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F77" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G77" s="8" t="s">
+      <c r="G77" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J77" s="8" t="s">
+      <c r="J77" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="6">
         <v>-0.91700000000000004</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F78" s="8" t="s">
+      <c r="F78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G78" s="8" t="s">
+      <c r="G78" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J78" s="8" t="s">
+      <c r="J78" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="6">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="E79" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F79" s="8" t="s">
+      <c r="F79" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G79" s="8" t="s">
+      <c r="G79" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H79" s="8" t="s">
+      <c r="H79" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J79" s="8" t="s">
+      <c r="J79" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="6">
         <v>5.7750000000000003E-2</v>
       </c>
-      <c r="E80" s="8" t="s">
+      <c r="E80" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F80" s="8" t="s">
+      <c r="F80" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G80" s="8" t="s">
+      <c r="G80" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H80" s="8" t="s">
+      <c r="H80" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J80" s="8" t="s">
+      <c r="J80" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="6">
         <v>3.2014499999999998E-4</v>
       </c>
-      <c r="E81" s="8" t="s">
+      <c r="E81" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F81" s="8" t="s">
+      <c r="F81" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G81" s="8" t="s">
+      <c r="G81" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H81" s="8" t="s">
+      <c r="H81" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J81" s="8" t="s">
+      <c r="J81" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="82" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:14" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>0</v>
@@ -4713,47 +4704,47 @@
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B86" s="11">
+      <c r="B86" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="9" t="s">
+      <c r="A87" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="9" t="s">
+      <c r="A88" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A89" s="9" t="s">
+      <c r="A89" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4802,261 +4793,261 @@
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A91" s="8" t="str">
+      <c r="A91" s="6" t="str">
         <f>B83</f>
         <v>[P+R] Coating</v>
       </c>
-      <c r="B91" s="8" t="str">
+      <c r="B91" s="6" t="str">
         <f>B84</f>
         <v>Coated spherical graphite</v>
       </c>
-      <c r="C91" s="8" t="str">
+      <c r="C91" s="6" t="str">
         <f>B85</f>
         <v>CN</v>
       </c>
-      <c r="D91" s="11">
+      <c r="D91" s="6">
         <v>1</v>
       </c>
-      <c r="E91" s="8" t="s">
+      <c r="E91" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F91" s="12" t="str">
+      <c r="F91" s="10" t="str">
         <f>F66</f>
         <v>Graphite</v>
       </c>
-      <c r="G91" s="8" t="s">
+      <c r="G91" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="6">
         <v>4.55</v>
       </c>
-      <c r="E92" s="8" t="s">
+      <c r="E92" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F92" s="8" t="s">
+      <c r="F92" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G92" s="8" t="s">
+      <c r="G92" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J92" s="8" t="s">
+      <c r="J92" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="6">
         <v>1.1205E-2</v>
       </c>
-      <c r="E93" s="8" t="s">
+      <c r="E93" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F93" s="8" t="s">
+      <c r="F93" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G93" s="8" t="s">
+      <c r="G93" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J93" s="8" t="s">
+      <c r="J93" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="C94" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D94" s="6">
         <v>0.05</v>
       </c>
-      <c r="E94" s="8" t="s">
+      <c r="E94" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F94" s="8" t="s">
+      <c r="F94" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G94" s="8" t="s">
+      <c r="G94" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J94" s="8" t="s">
+      <c r="J94" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B95" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="C95" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D95" s="8">
+      <c r="D95" s="6">
         <v>1.5E-3</v>
       </c>
-      <c r="E95" s="8" t="s">
+      <c r="E95" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F95" s="8" t="s">
+      <c r="F95" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G95" s="8" t="s">
+      <c r="G95" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J95" s="8" t="s">
+      <c r="J95" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="C96" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="6">
         <v>1.7978000000000001</v>
       </c>
-      <c r="E96" s="8" t="s">
+      <c r="E96" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F96" s="8" t="s">
+      <c r="F96" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G96" s="8" t="s">
+      <c r="G96" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J96" s="8" t="s">
+      <c r="J96" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D97" s="8">
+      <c r="D97" s="6">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="E97" s="8" t="s">
+      <c r="E97" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F97" s="8" t="s">
+      <c r="F97" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G97" s="8" t="s">
+      <c r="G97" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J97" s="8" t="s">
+      <c r="J97" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C98" s="8" t="s">
+      <c r="C98" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D98" s="8">
+      <c r="D98" s="6">
         <v>-4.5499999999999999E-2</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E98" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F98" s="8" t="s">
+      <c r="F98" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G98" s="8" t="s">
+      <c r="G98" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J98" s="8" t="s">
+      <c r="J98" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D99" s="8">
+      <c r="D99" s="6">
         <v>6.2406999999999997E-2</v>
       </c>
-      <c r="E99" s="8" t="s">
+      <c r="E99" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F99" s="8" t="s">
+      <c r="F99" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G99" s="8" t="s">
+      <c r="G99" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H99" s="8" t="s">
+      <c r="H99" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J99" s="8" t="s">
+      <c r="J99" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D100" s="8">
+      <c r="D100" s="6">
         <v>1.5E-3</v>
       </c>
-      <c r="E100" s="8" t="s">
+      <c r="E100" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F100" s="8" t="s">
+      <c r="F100" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G100" s="8" t="s">
+      <c r="G100" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H100" s="8" t="s">
+      <c r="H100" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J100" s="8" t="s">
+      <c r="J100" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="101" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="101" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
         <v>0</v>
@@ -5066,47 +5057,47 @@
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
+      <c r="A103" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A104" s="9" t="s">
+      <c r="A104" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B104" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
+      <c r="A105" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B105" s="11">
+      <c r="B105" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A106" s="9" t="s">
+      <c r="A106" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B106" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A107" s="9" t="s">
+      <c r="A107" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="B107" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A108" s="9" t="s">
+      <c r="A108" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5155,169 +5146,169 @@
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A110" s="8" t="str">
+      <c r="A110" s="6" t="str">
         <f>B102</f>
         <v>Graphite ore mining in China/Heilongjiang and natural graphite production in China/Shandong</v>
       </c>
-      <c r="B110" s="8" t="str">
+      <c r="B110" s="6" t="str">
         <f>B103</f>
         <v>Battery-grade graphite</v>
       </c>
-      <c r="C110" s="8" t="str">
+      <c r="C110" s="6" t="str">
         <f>B104</f>
         <v>CN</v>
       </c>
-      <c r="D110" s="11">
+      <c r="D110" s="6">
         <v>1</v>
       </c>
-      <c r="E110" s="8" t="s">
+      <c r="E110" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F110" s="12" t="str">
+      <c r="F110" s="10" t="str">
         <f>F91</f>
         <v>Graphite</v>
       </c>
-      <c r="G110" s="8" t="s">
+      <c r="G110" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A111" s="8" t="str">
+      <c r="A111" s="6" t="str">
         <f>A91</f>
         <v>[P+R] Coating</v>
       </c>
-      <c r="B111" s="8" t="str">
+      <c r="B111" s="6" t="str">
         <f>B91</f>
         <v>Coated spherical graphite</v>
       </c>
-      <c r="C111" s="8" t="str">
+      <c r="C111" s="6" t="str">
         <f>C91</f>
         <v>CN</v>
       </c>
-      <c r="D111" s="8">
+      <c r="D111" s="6">
         <v>1</v>
       </c>
-      <c r="E111" s="8" t="str">
+      <c r="E111" s="6" t="str">
         <f>E91</f>
         <v>kilogram</v>
       </c>
-      <c r="F111" s="12" t="str">
+      <c r="F111" s="10" t="str">
         <f>F91</f>
         <v>Graphite</v>
       </c>
-      <c r="G111" s="8" t="s">
+      <c r="G111" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A112" s="8" t="str">
+      <c r="A112" s="6" t="str">
         <f>A66</f>
         <v>[P+R] Purification</v>
       </c>
-      <c r="B112" s="8" t="str">
+      <c r="B112" s="6" t="str">
         <f>B66</f>
         <v>Purified spherical graphite</v>
       </c>
-      <c r="C112" s="8" t="str">
+      <c r="C112" s="6" t="str">
         <f>C66</f>
         <v>CN</v>
       </c>
-      <c r="D112" s="8">
+      <c r="D112" s="6">
         <v>1.01</v>
       </c>
-      <c r="E112" s="8" t="str">
+      <c r="E112" s="6" t="str">
         <f>E66</f>
         <v>kilogram</v>
       </c>
-      <c r="F112" s="12" t="str">
+      <c r="F112" s="10" t="str">
         <f>F66</f>
         <v>Graphite</v>
       </c>
-      <c r="G112" s="8" t="s">
+      <c r="G112" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="8" t="str">
+      <c r="A113" s="6" t="str">
         <f>A53</f>
         <v>[P+R] Spheronisation</v>
       </c>
-      <c r="B113" s="8" t="str">
+      <c r="B113" s="6" t="str">
         <f>B53</f>
         <v>Spherical graphite</v>
       </c>
-      <c r="C113" s="8" t="str">
+      <c r="C113" s="6" t="str">
         <f>C53</f>
         <v>CN</v>
       </c>
-      <c r="D113" s="8">
+      <c r="D113" s="6">
         <v>1.1413</v>
       </c>
-      <c r="E113" s="8" t="str">
+      <c r="E113" s="6" t="str">
         <f>E53</f>
         <v>kilogram</v>
       </c>
-      <c r="F113" s="12" t="str">
+      <c r="F113" s="10" t="str">
         <f>F53</f>
         <v>Graphite</v>
       </c>
-      <c r="G113" s="8" t="s">
+      <c r="G113" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="8" t="str">
+      <c r="A114" s="6" t="str">
         <f>A29</f>
         <v>[C] Flotation</v>
       </c>
-      <c r="B114" s="8" t="str">
+      <c r="B114" s="6" t="str">
         <f>B29</f>
         <v>Graphite concentrate</v>
       </c>
-      <c r="C114" s="8" t="str">
+      <c r="C114" s="6" t="str">
         <f>C29</f>
         <v>CN</v>
       </c>
-      <c r="D114" s="8">
+      <c r="D114" s="6">
         <v>2.5336860000000003</v>
       </c>
-      <c r="E114" s="8" t="str">
+      <c r="E114" s="6" t="str">
         <f>E29</f>
         <v>kilogram</v>
       </c>
-      <c r="F114" s="12" t="str">
+      <c r="F114" s="10" t="str">
         <f>F29</f>
         <v>Graphite</v>
       </c>
-      <c r="G114" s="8" t="s">
+      <c r="G114" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="8" t="str">
+      <c r="A115" s="6" t="str">
         <f>A9</f>
         <v>[M] Graphite ore mining</v>
       </c>
-      <c r="B115" s="8" t="str">
+      <c r="B115" s="6" t="str">
         <f>B9</f>
         <v>Graphite ore</v>
       </c>
-      <c r="C115" s="8" t="str">
+      <c r="C115" s="6" t="str">
         <f>C9</f>
         <v>CN</v>
       </c>
-      <c r="D115" s="8">
+      <c r="D115" s="6">
         <v>24.298048740000002</v>
       </c>
-      <c r="E115" s="8" t="str">
+      <c r="E115" s="6" t="str">
         <f>E9</f>
         <v>kilogram</v>
       </c>
-      <c r="F115" s="12" t="str">
+      <c r="F115" s="10" t="str">
         <f>F9</f>
         <v>Graphite</v>
       </c>
-      <c r="G115" s="8" t="s">
+      <c r="G115" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -5334,21 +5325,21 @@
   <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="48" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -5360,47 +5351,47 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -5449,547 +5440,547 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="str">
+      <c r="A9" s="6" t="str">
         <f>B1</f>
         <v>[P+R] Synthetic graphite production</v>
       </c>
-      <c r="B9" s="8" t="str">
+      <c r="B9" s="6" t="str">
         <f>B2</f>
         <v>Battery-grade graphite</v>
       </c>
-      <c r="C9" s="8" t="str">
+      <c r="C9" s="6" t="str">
         <f>B3</f>
         <v>CN</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="6">
         <v>1</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="12" t="str">
+      <c r="F9" s="10" t="str">
         <f>Graphite_Market_GLO!B1</f>
         <v>Graphite</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>2.0299999999999998</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <v>1.88</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="6">
         <v>0.75600000000000001</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <v>0.27</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>16</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <v>12.74</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>-0.26</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>3.33</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="6">
         <v>0.97200000000000009</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="6">
         <v>0.05</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="6">
         <v>0.17</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="6">
         <v>0.21</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="6">
         <v>7.74</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="6">
         <v>1E-3</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="6">
         <v>0.02</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <v>0.05</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="6">
         <v>0.02</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="J26" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="6">
         <v>0.108</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J27" s="8" t="s">
+      <c r="J27" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="6">
         <v>0.72</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J28" s="8" t="s">
+      <c r="J28" s="6" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="6">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J29" s="8" t="s">
+      <c r="J29" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>0</v>
@@ -5999,47 +5990,47 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
+      <c r="A36" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6088,58 +6079,58 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="str">
+      <c r="A39" s="6" t="str">
         <f>B31</f>
         <v>Synthetic graphite production in China</v>
       </c>
-      <c r="B39" s="8" t="str">
+      <c r="B39" s="6" t="str">
         <f>B32</f>
         <v>Battery-grade graphite</v>
       </c>
-      <c r="C39" s="8" t="str">
+      <c r="C39" s="6" t="str">
         <f>B33</f>
         <v>CN</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="6">
         <v>1</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F39" s="12" t="str">
+      <c r="F39" s="10" t="str">
         <f>F9</f>
         <v>Graphite</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="str">
+      <c r="A40" s="6" t="str">
         <f>A9</f>
         <v>[P+R] Synthetic graphite production</v>
       </c>
-      <c r="B40" s="8" t="str">
+      <c r="B40" s="6" t="str">
         <f t="shared" ref="B40:F40" si="0">B9</f>
         <v>Battery-grade graphite</v>
       </c>
-      <c r="C40" s="8" t="str">
+      <c r="C40" s="6" t="str">
         <f t="shared" si="0"/>
         <v>CN</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="E40" s="8" t="str">
+      <c r="E40" s="6" t="str">
         <f t="shared" si="0"/>
         <v>kilogram</v>
       </c>
-      <c r="F40" s="12" t="str">
+      <c r="F40" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Graphite</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -6158,17 +6149,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004741122952C13D46BBBC92EEAE11CF32" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="d96b5fa62e5213e7d24e66b2bac0c378">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d78c010b-218d-4be4-b2d9-423b1f51aae5" xmlns:ns3="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c2e8fc9a9c70fab2c0f7259df75af726" ns2:_="" ns3:_="">
     <xsd:import namespace="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
@@ -6391,6 +6371,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC223732-7A84-4201-81E0-F4F10B7197AE}">
   <ds:schemaRefs>
@@ -6400,17 +6391,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B5D110D-E837-4E58-A07A-E5D7A5B90784}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
-    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B185980D-96BE-4271-BA9B-881F9B7C5EB4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6427,4 +6407,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B5D110D-E837-4E58-A07A-E5D7A5B90784}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
+    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/LCIs/Lai_2025/Graphite_LCIs_BW_Final_v1.xlsx
+++ b/data/LCIs/Lai_2025/Graphite_LCIs_BW_Final_v1.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="178" documentId="8_{4E3DD59C-3AFA-4D66-BAD6-4D8B482B0214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE8171B-4DE3-4F15-97E4-E0BCC54C54EB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" r:id="rId1"/>
@@ -6140,12 +6140,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6372,20 +6374,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC223732-7A84-4201-81E0-F4F10B7197AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B5D110D-E837-4E58-A07A-E5D7A5B90784}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
+    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6410,12 +6413,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B5D110D-E837-4E58-A07A-E5D7A5B90784}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC223732-7A84-4201-81E0-F4F10B7197AE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
-    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>